--- a/output/xlsform_hab5-7.xlsx
+++ b/output/xlsform_hab5-7.xlsx
@@ -49645,7 +49645,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C59"/>
+  <dimension ref="A1:C60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -49962,12 +49962,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>afw</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>s</t>
+          <t>afw.</t>
         </is>
       </c>
     </row>
@@ -49979,12 +49979,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>zs</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>r</t>
+          <t>zs (&lt;3 ex.)</t>
         </is>
       </c>
     </row>
@@ -49996,12 +49996,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>s</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>o</t>
+          <t>s (4-10 ex.)</t>
         </is>
       </c>
     </row>
@@ -50013,12 +50013,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>wt</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>f</t>
+          <t>wt (10-50 ex.)</t>
         </is>
       </c>
     </row>
@@ -50030,12 +50030,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5_10perc</t>
+          <t>t</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>5-10%</t>
+          <t>t (&gt;50 ex.)</t>
         </is>
       </c>
     </row>
@@ -50047,12 +50047,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>10_20perc</t>
+          <t>5_10perc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>10-20%</t>
+          <t>5-10</t>
         </is>
       </c>
     </row>
@@ -50064,12 +50064,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>20_30perc</t>
+          <t>10_20perc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>20-30%</t>
+          <t>10-20</t>
         </is>
       </c>
     </row>
@@ -50081,12 +50081,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>30_40perc</t>
+          <t>20_30perc</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>30-40%</t>
+          <t>20-30</t>
         </is>
       </c>
     </row>
@@ -50098,12 +50098,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>40_50perc</t>
+          <t>30_40perc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>40-50%</t>
+          <t>30-40</t>
         </is>
       </c>
     </row>
@@ -50115,12 +50115,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>50_60perc</t>
+          <t>40_50perc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>50-60%</t>
+          <t>40-50</t>
         </is>
       </c>
     </row>
@@ -50132,12 +50132,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>60_70perc</t>
+          <t>50_60perc</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>60-70%</t>
+          <t>50-60</t>
         </is>
       </c>
     </row>
@@ -50149,12 +50149,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>70_80perc</t>
+          <t>60_70perc</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>70-80%</t>
+          <t>60-70</t>
         </is>
       </c>
     </row>
@@ -50166,12 +50166,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>80_90perc</t>
+          <t>70_80perc</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>80-90%</t>
+          <t>70-80</t>
         </is>
       </c>
     </row>
@@ -50183,12 +50183,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>90_95perc</t>
+          <t>80_90perc</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>90-95%</t>
+          <t>80-90</t>
         </is>
       </c>
     </row>
@@ -50200,29 +50200,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>95_100perc</t>
+          <t>90_95perc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>95-100%</t>
+          <t>90-95</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>lijst_subhabitats</t>
+          <t>LSVI</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5130_hei</t>
+          <t>95_100perc</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>5130_HEI</t>
+          <t>95-100</t>
         </is>
       </c>
     </row>
@@ -50234,12 +50234,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5130_kalk</t>
+          <t>5130_hei</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>5130_KALK</t>
+          <t>5130_HEI</t>
         </is>
       </c>
     </row>
@@ -50251,12 +50251,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>7110</t>
+          <t>5130_kalk</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>7110</t>
+          <t>5130_KALK</t>
         </is>
       </c>
     </row>
@@ -50268,12 +50268,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>7140_base</t>
+          <t>7110</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>7140_BASE</t>
+          <t>7110</t>
         </is>
       </c>
     </row>
@@ -50285,12 +50285,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>7140_meso</t>
+          <t>7140_base</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>7140_MESO</t>
+          <t>7140_BASE</t>
         </is>
       </c>
     </row>
@@ -50302,12 +50302,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>7140_mrd</t>
+          <t>7140_meso</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>7140_MRD</t>
+          <t>7140_MESO</t>
         </is>
       </c>
     </row>
@@ -50319,12 +50319,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>7140_oli</t>
+          <t>7140_mrd</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>7140_OLI</t>
+          <t>7140_MRD</t>
         </is>
       </c>
     </row>
@@ -50336,12 +50336,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>7150</t>
+          <t>7140_oli</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>7150</t>
+          <t>7140_OLI</t>
         </is>
       </c>
     </row>
@@ -50353,12 +50353,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>7210</t>
+          <t>7150</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>7210</t>
+          <t>7150</t>
         </is>
       </c>
     </row>
@@ -50370,12 +50370,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>7220</t>
+          <t>7210</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>7220</t>
+          <t>7210</t>
         </is>
       </c>
     </row>
@@ -50387,12 +50387,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>7230</t>
+          <t>7220</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>7230</t>
+          <t>7220</t>
         </is>
       </c>
     </row>
@@ -50404,12 +50404,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>6120</t>
+          <t>7230</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>6120</t>
+          <t>7230</t>
         </is>
       </c>
     </row>
@@ -50421,12 +50421,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>6210</t>
+          <t>6120</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>6210</t>
+          <t>6120</t>
         </is>
       </c>
     </row>
@@ -50438,12 +50438,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>6230_hmo</t>
+          <t>6210</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>6230_HMO</t>
+          <t>6210</t>
         </is>
       </c>
     </row>
@@ -50455,12 +50455,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>6230_ha</t>
+          <t>6230_hmo</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>6230_HA</t>
+          <t>6230_HMO</t>
         </is>
       </c>
     </row>
@@ -50472,12 +50472,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>6230_hn</t>
+          <t>6230_ha</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>6230_HN</t>
+          <t>6230_HA</t>
         </is>
       </c>
     </row>
@@ -50489,12 +50489,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>6230_hnk</t>
+          <t>6230_hn</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>6230_HNK</t>
+          <t>6230_HN</t>
         </is>
       </c>
     </row>
@@ -50506,12 +50506,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>6430_bz</t>
+          <t>6230_hnk</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>6430_BZ</t>
+          <t>6230_HNK</t>
         </is>
       </c>
     </row>
@@ -50523,12 +50523,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>6430_hf</t>
+          <t>6430_bz</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>6430_HF</t>
+          <t>6430_BZ</t>
         </is>
       </c>
     </row>
@@ -50540,12 +50540,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>6430_hw</t>
+          <t>6430_hf</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>6430_HW</t>
+          <t>6430_HF</t>
         </is>
       </c>
     </row>
@@ -50557,12 +50557,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>6430_mr</t>
+          <t>6430_hw</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>6430_MR</t>
+          <t>6430_HW</t>
         </is>
       </c>
     </row>
@@ -50574,12 +50574,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>6510_hu</t>
+          <t>6430_mr</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>6510_HU</t>
+          <t>6430_MR</t>
         </is>
       </c>
     </row>
@@ -50591,12 +50591,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>6510_hus</t>
+          <t>6510_hu</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>6510_HUS</t>
+          <t>6510_HU</t>
         </is>
       </c>
     </row>
@@ -50608,12 +50608,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>6510_huk</t>
+          <t>6510_hus</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>6510_HUK</t>
+          <t>6510_HUS</t>
         </is>
       </c>
     </row>
@@ -50625,12 +50625,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>6410</t>
+          <t>6510_huk</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>6410</t>
+          <t>6510_HUK</t>
         </is>
       </c>
     </row>
@@ -50642,10 +50642,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
+          <t>6410</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>6410</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>lijst_subhabitats</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
           <t>6510_hua</t>
         </is>
       </c>
-      <c r="C59" t="inlineStr">
+      <c r="C60" t="inlineStr">
         <is>
           <t>6510_HUA</t>
         </is>
